--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>266</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>4.705475696616046</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>314</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>2.934292454480971</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>235</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>4.157093190619439</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>330</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>3.083810541333504</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>308</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>5.448445543450159</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>348</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>3.252018389042604</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>229</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>4.050954641071709</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>328</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>3.065120780476937</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>257</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>4.546267872294451</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>309</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>2.887568052339554</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>273</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>4.829304004421732</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>349</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>3.261363269470888</v>
       </c>
@@ -5512,16 +5476,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O26" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R26" t="n">
-        <v>4.33399077319899</v>
+        <v>4.422439564488766</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5674,10 +5635,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O27" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>351</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>3.280053030327454</v>
       </c>
@@ -6304,16 +6262,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="R30" t="n">
-        <v>0.05306927477386519</v>
+        <v>1.026005978961394</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6466,10 +6421,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6811,7 +6766,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4145</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -5476,13 +5476,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O26" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R26" t="n">
-        <v>4.422439564488766</v>
+        <v>4.440129322746721</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O27" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="O30" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="R30" t="n">
-        <v>1.026005978961394</v>
+        <v>2.158150507470518</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="O31" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4205</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="O30" t="n">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="R30" t="n">
-        <v>2.158150507470518</v>
+        <v>3.573331168106922</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="O31" t="n">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4270</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="O30" t="n">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="R30" t="n">
-        <v>3.573331168106922</v>
+        <v>5.094650378291058</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="O31" t="n">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6583,6 +6583,399 @@
         </is>
       </c>
       <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>MRSA</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS MRSA surveillance category.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -6621,7 +7014,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -6704,7 +7097,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -6714,7 +7107,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -6734,7 +7127,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -6766,7 +7159,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4350</v>
+        <v>4436</v>
       </c>
     </row>
     <row r="16">
